--- a/data/trans_dic/Predimed_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,76</t>
+          <t>16,31; 23,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 24,81</t>
+          <t>18,24; 25,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 23,3</t>
+          <t>18,33; 23,25</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,9; 21,46</t>
+          <t>13,89; 21,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,81; 27,24</t>
+          <t>19,65; 26,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,54</t>
+          <t>17,59; 22,92</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 22,33</t>
+          <t>4,66; 22,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 31,43</t>
+          <t>20,43; 32,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 23,15</t>
+          <t>6,39; 23,25</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 22,05</t>
+          <t>16,52; 22,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 21,57</t>
+          <t>8,18; 21,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 20,52</t>
+          <t>12,1; 20,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,94</t>
+          <t>8,36; 14,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 31,48</t>
+          <t>14,82; 31,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 24,35</t>
+          <t>13,3; 24,17</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,67</t>
+          <t>3,35; 15,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,51</t>
+          <t>9,94; 14,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 13,5</t>
+          <t>9,18; 13,36</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,88</t>
+          <t>12,19; 18,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,12; 20,86</t>
+          <t>14,61; 20,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,84</t>
+          <t>14,65; 18,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80567; 114928</t>
+          <t>78895; 114160</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79565; 107473</t>
+          <t>79008; 108654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166314; 213611</t>
+          <t>168006; 213161</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59500; 91863</t>
+          <t>59465; 90668</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73497; 101075</t>
+          <t>72899; 99523</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138882; 180170</t>
+          <t>140603; 183210</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29766; 143645</t>
+          <t>29950; 142994</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32129; 49555</t>
+          <t>32213; 51364</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56581; 185440</t>
+          <t>51185; 186235</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>162997; 210681</t>
+          <t>157848; 213333</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73187; 202507</t>
+          <t>76821; 202386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213341; 388655</t>
+          <t>229161; 388400</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36900; 65488</t>
+          <t>36661; 64816</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>116330; 250205</t>
+          <t>117826; 250951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166408; 300339</t>
+          <t>164042; 298051</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6614; 33158</t>
+          <t>6659; 31425</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69937; 100642</t>
+          <t>68945; 99722</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81674; 120541</t>
+          <t>81956; 119289</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>377104; 562703</t>
+          <t>383536; 567668</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>512276; 707069</t>
+          <t>495061; 697540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>963523; 1231534</t>
+          <t>957674; 1226099</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 23,6</t>
+          <t>16,73; 24,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 25,09</t>
+          <t>18,26; 24,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 23,25</t>
+          <t>18,33; 23,5</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 21,18</t>
+          <t>14,41; 22,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 26,82</t>
+          <t>20,31; 27,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,92</t>
+          <t>18,06; 23,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,23</t>
+          <t>18,22; 25,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 32,58</t>
+          <t>19,25; 30,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 23,25</t>
+          <t>19,39; 25,91</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 22,33</t>
+          <t>17,1; 22,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,56</t>
+          <t>18,28; 22,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 20,51</t>
+          <t>18,18; 22,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,78</t>
+          <t>7,7; 13,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 31,57</t>
+          <t>15,33; 20,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 24,17</t>
+          <t>12,73; 16,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 15,8</t>
+          <t>3,3; 15,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,37</t>
+          <t>10,03; 14,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 13,36</t>
+          <t>9,19; 13,29</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,03</t>
+          <t>16,1; 18,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,61; 20,58</t>
+          <t>17,54; 19,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,76</t>
+          <t>17,14; 18,98</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>108420</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189330</t>
+          <t>208914</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78895; 114160</t>
+          <t>88015; 129364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79008; 108654</t>
+          <t>86387; 117579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168006; 213161</t>
+          <t>183169; 234807</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73498</t>
+          <t>81418</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86318</t>
+          <t>96806</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159817</t>
+          <t>178223</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59465; 90668</t>
+          <t>65905; 100850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72899; 99523</t>
+          <t>83237; 112091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140603; 183210</t>
+          <t>156660; 201981</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83131</t>
+          <t>96766</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123245</t>
+          <t>139881</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29950; 142994</t>
+          <t>81039; 115624</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32213; 51364</t>
+          <t>33961; 53416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51185; 186235</t>
+          <t>120489; 160945</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>183584</t>
+          <t>205991</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334842</t>
+          <t>374363</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157848; 213333</t>
+          <t>178893; 235702</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76821; 202386</t>
+          <t>149609; 188138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229161; 388400</t>
+          <t>339048; 411669</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49680</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>135089</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>188920</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36661; 64816</t>
+          <t>40005; 70964</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117826; 250951</t>
+          <t>119184; 155876</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164042; 298051</t>
+          <t>165187; 211300</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>92775</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99121</t>
+          <t>106903</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6659; 31425</t>
+          <t>6544; 30175</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68945; 99722</t>
+          <t>77288; 108768</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81956; 119289</t>
+          <t>89104; 128855</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>502137</t>
+          <t>560553</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>612343</t>
+          <t>636651</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1114480</t>
+          <t>1197204</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>383536; 567668</t>
+          <t>514101; 605695</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>495061; 697540</t>
+          <t>601094; 678505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>957674; 1226099</t>
+          <t>1134735; 1256075</t>
         </is>
       </c>
     </row>
